--- a/docs/test-cases/SPM-27_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-27_Test_Cases.xlsx
@@ -8,26 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samis\OneDrive\Documents\Is212spm\IS212-1\docs\test-cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_B9682CCA0321CFEED1415E3E0547BAF6AB5276F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F28345C-C84D-4348-888D-978248DDDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="TC01" sheetId="2" r:id="rId2"/>
-    <sheet name="TC02" sheetId="3" r:id="rId3"/>
-    <sheet name="TC03" sheetId="4" r:id="rId4"/>
-    <sheet name="TC04" sheetId="5" r:id="rId5"/>
-    <sheet name="TC05" sheetId="6" r:id="rId6"/>
-    <sheet name="TC06" sheetId="7" r:id="rId7"/>
-    <sheet name="TC07" sheetId="8" r:id="rId8"/>
+    <sheet name="TC01" sheetId="3" r:id="rId2"/>
+    <sheet name="TC02" sheetId="4" r:id="rId3"/>
+    <sheet name="TC03" sheetId="5" r:id="rId4"/>
+    <sheet name="TC04" sheetId="6" r:id="rId5"/>
+    <sheet name="TC05" sheetId="7" r:id="rId6"/>
+    <sheet name="TC06" sheetId="8" r:id="rId7"/>
+    <sheet name="TC07" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="96">
   <si>
     <t>Story</t>
   </si>
@@ -89,7 +89,7 @@
     <t>SPM-27-TC03</t>
   </si>
   <si>
-    <t>Choosing 'Keep request' in the withdraw dialog leaves the status unchanged</t>
+    <t>Choosing 'Keep request' in the withdrawal dialog leaves the status unchanged</t>
   </si>
   <si>
     <t>AC2</t>
@@ -107,7 +107,7 @@
     <t>SPM-27-TC04</t>
   </si>
   <si>
-    <t>Organiser withdraws a Submitted or Under review request</t>
+    <t>Coordinator records a withdrawal and the organiser sees Withdrawn</t>
   </si>
   <si>
     <t>AC2, AC3</t>
@@ -119,7 +119,7 @@
     <t>SPM-27-TC05</t>
   </si>
   <si>
-    <t>Organiser has no way to change the status of an event from Approved onwards</t>
+    <t>Organiser has no way to change the status of their event</t>
   </si>
   <si>
     <t>AC4</t>
@@ -134,10 +134,7 @@
     <t>SPM-27-TC06</t>
   </si>
   <si>
-    <t>Only the event's organiser is offered 'Withdraw request'</t>
-  </si>
-  <si>
-    <t>AC3</t>
+    <t>Only the assigned coordinator is offered 'Record withdrawal'</t>
   </si>
   <si>
     <t>TC07</t>
@@ -174,15 +171,18 @@
     <t>SPM-27-TC02
 SPM-27-TC03
 SPM-27-TC04
+SPM-27-TC06
 SPM-27-TC07</t>
   </si>
   <si>
+    <t>AC3</t>
+  </si>
+  <si>
     <t>The system displays appropriate statuses such as Submitted, Under Review, Approved, Planning, Confirmed, Completed, Rejected, Postponed, Withdrawn or Cancelled.</t>
   </si>
   <si>
     <t>SPM-27-TC01
-SPM-27-TC04
-SPM-27-TC06</t>
+SPM-27-TC04</t>
   </si>
   <si>
     <t>The Event Organiser cannot manually change the event status.</t>
@@ -203,8 +203,9 @@
 src/app/venues/search/page.tsx
 docs/ConnectSphere_Status_Lifecycle.drawio
 docs/PERMISSIONS.md
-scripts/seed-spm30.ts
-prisma/seed.ts</t>
+scripts/seed-spm27.ts
+prisma/seed.ts
+src/app/queue/page.tsx</t>
   </si>
   <si>
     <t>Item</t>
@@ -220,8 +221,7 @@
     <t>Test Steps</t>
   </si>
   <si>
-    <t>1. Click 'My Events' in the sidebar
-2. Find each of the 14 SPM27 events in the list and read its Status column</t>
+    <t>1. Click 'My Events' in the sidebar</t>
   </si>
   <si>
     <t>Test Data</t>
@@ -233,9 +233,7 @@
     <t>Expected Result</t>
   </si>
   <si>
-    <t>Each of the 14 SPM27 events shows a coloured status badge with exactly the label listed in Test data, so all 10 statuses appear: Submitted, Under review, Approved, Planning, Confirmed, Completed, Rejected, Postponed, Withdrawn, Cancelled (some on more than one event).
-No status is shown as a raw value such as 'under_review'.
-Only Bayu Energy Partners events are listed; no other company's events appear.</t>
+    <t>Step 1: Each of the 14 SPM27 events shows a coloured status badge with exactly the label listed in Test data, so all 10 statuses appear: Submitted, Under review, Approved, Planning, Confirmed, Completed, Rejected, Postponed, Withdrawn, Cancelled (some on more than one event). No status is shown as a raw value such as 'under_review'. Only Bayu Energy Partners events are listed; no other company's events appear.</t>
   </si>
   <si>
     <t>Created By</t>
@@ -253,133 +251,155 @@
     <t>Pass/Fail/Not Executed/Blocked</t>
   </si>
   <si>
-    <t>Pass</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Executed by</t>
   </si>
   <si>
-    <t>Sammi</t>
-  </si>
-  <si>
     <t>Date of Execution</t>
   </si>
   <si>
-    <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder just before this case.
+    <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder before and after this case.
 'SPM27 Bayu Investor Day' is Submitted with no coordinator.
 Accounts: Hakim Zulkifli (hakim.zulkifli@bayuenergypa.com / password123), Event Organiser; Grace Lim (grace.lim@connectsphere.com / password123), Event Operations Manager.</t>
   </si>
   <si>
-    <t>1. Log in as Hakim Zulkifli and open 'SPM27 Bayu Investor Day' from 'My Events'
-2. Read the badge under the title and the 'Status' row in the 'Details' card
-3. Log out and log in as Grace Lim
-4. Click 'Assignments' in the sidebar
-5. On the 'SPM27 Bayu Investor Day' row, choose 'Hui Shan Neo' in 'Assign to' and click 'Assign'
+    <t>1. Log in as Hakim Zulkifli
+2. Click 'My Events' in the sidebar
+3. Open 'SPM27 Bayu Investor Day'
+4. Log out and log in as Grace Lim
+5. Click 'Assignments' in the sidebar
+6. On the 'SPM27 Bayu Investor Day' row, choose 'Hui Shan Neo' in 'Assign to'
+7. Click 'Assign'
+8. Log out and log in as Hakim Zulkifli
+9. Click 'My Events' in the sidebar
+10. Open 'SPM27 Bayu Investor Day'</t>
+  </si>
+  <si>
+    <t>Event: SPM27 Bayu Investor Day | Coordinator: Hui Shan Neo</t>
+  </si>
+  <si>
+    <t>Step 3: The badge under the title and the Details 'Status' row both read 'Submitted'.
+Step 10: The badge and the Details 'Status' row both read 'Under review'.</t>
+  </si>
+  <si>
+    <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder just before this case.
+'SPM27 Bayu Grid Workshop' is Under review, coordinator Hui Shan Neo.
+Logged in as Hui Shan Neo (huishan.neo@connectsphere.com / password123), Event Coordinator.
+Withdrawal follows customer clarification #103: the organiser asks the Event Coordinator outside the system, and the assigned coordinator records the withdrawal while the request is Under review. Withdrawn is final.</t>
+  </si>
+  <si>
+    <t>1. Click 'All Events' in the sidebar
+2. Open 'SPM27 Bayu Grid Workshop'
+3. Click 'Record withdrawal'
+4. In the dialog, click 'Keep request'
+5. Reload the page</t>
+  </si>
+  <si>
+    <t>Event: SPM27 Bayu Grid Workshop (Under review)</t>
+  </si>
+  <si>
+    <t>Step 3: A dialog titled 'Record this withdrawal?' appears.
+Step 4: The dialog closes.
+Step 5: The badge still reads 'Under review' and the 'Record withdrawal' button is still shown.</t>
+  </si>
+  <si>
+    <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder before and after this case (SPM-27-TC03 does not change the data, so this case can run straight after it).
+'SPM27 Bayu Grid Workshop' is Under review, coordinator Hui Shan Neo.
+Accounts: Hui Shan Neo (huishan.neo@connectsphere.com / password123), Event Coordinator; Hakim Zulkifli (hakim.zulkifli@bayuenergypa.com / password123), Event Organiser.
+Withdrawal follows customer clarification #103: the organiser asks the Event Coordinator outside the system, and the assigned coordinator records the withdrawal while the request is Under review. Withdrawn is final.</t>
+  </si>
+  <si>
+    <t>1. Log in as Hui Shan Neo
+2. Click 'All Events' in the sidebar
+3. Open 'SPM27 Bayu Grid Workshop'
+4. Click 'Record withdrawal'
+5. In the dialog 'Record this withdrawal?', click 'Record withdrawal'
 6. Log out and log in as Hakim Zulkifli
-7. Click 'My Events' and open 'SPM27 Bayu Investor Day'</t>
-  </si>
-  <si>
-    <t>Event: SPM27 Bayu Investor Day | Coordinator: Hui Shan Neo</t>
-  </si>
-  <si>
-    <t>Before the assignment, the header badge and the Details 'Status' row both read 'Submitted'.
-After the assignment, both read 'Under review'.</t>
-  </si>
-  <si>
-    <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder just before this case.
-'SPM27 Bayu Safety Briefing' is Submitted.
-Logged in as Hakim Zulkifli (hakim.zulkifli@bayuenergypa.com / password123).</t>
-  </si>
-  <si>
-    <t>1. Click 'My Events' and open 'SPM27 Bayu Safety Briefing'
-2. Click 'Withdraw request'
-3. In the dialog 'Withdraw this request?', click 'Keep request'
-4. Reload the page</t>
-  </si>
-  <si>
-    <t>Event: SPM27 Bayu Safety Briefing (Submitted)</t>
-  </si>
-  <si>
-    <t>The dialog closes.
-After reloading, the badge still reads 'Submitted' and the 'Withdraw request' button is still shown.</t>
-  </si>
-  <si>
-    <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder (TC03 does not change the data, so it can run straight after TC03).
-'SPM27 Bayu Safety Briefing' is Submitted; 'SPM27 Bayu Grid Workshop' is Under review (coordinator Hui Shan Neo).
-Logged in as Hakim Zulkifli (hakim.zulkifli@bayuenergypa.com / password123).
-Team decision: see TC03.</t>
-  </si>
-  <si>
-    <t>1. Click 'My Events' and open 'SPM27 Bayu Safety Briefing'
-2. Click 'Withdraw request'
-3. In the dialog 'Withdraw this request?', click 'Withdraw request'
-4. Repeat steps 1-3 for 'SPM27 Bayu Grid Workshop'</t>
-  </si>
-  <si>
-    <t>Submitted: SPM27 Bayu Safety Briefing | Under review: SPM27 Bayu Grid Workshop</t>
-  </si>
-  <si>
-    <t>For each event, the success message 'Your request has been withdrawn.' is shown and the status badge changes to 'Withdrawn'.</t>
+7. Click 'My Events' in the sidebar
+8. Open 'SPM27 Bayu Grid Workshop'</t>
+  </si>
+  <si>
+    <t>Step 5: The message 'The withdrawal has been recorded.' is shown, the badge changes to 'Withdrawn' and the 'Record withdrawal' button is gone.
+Step 8: The badge and the Details 'Status' row read 'Withdrawn'.</t>
   </si>
   <si>
     <t>Test data loaded: run `npm run fixtures:spm27` from the project folder if it has not been run for this test pass.
 Logged in as Hakim Zulkifli (hakim.zulkifli@bayuenergypa.com / password123).</t>
   </si>
   <si>
-    <t>1. Click 'My Events' and open 'SPM27 Bayu Supplier Day'
-2. Look for 'Withdraw request' or any button, dropdown or field that changes the status
-3. Repeat for every other event in Test data</t>
-  </si>
-  <si>
-    <t>Approved (first status after the withdraw window closes): SPM27 Bayu Supplier Day | Planning: SPM27 Bayu Leadership Retreat | Confirmed: SPM27 Bayu Annual Conference | Postponed: SPM27 Bayu Community Fair | Completed: SPM27 Bayu Graduate Induction | Rejected: SPM27 Bayu Overnight Site Visit | Cancelled: SPM27 Bayu Product Showcase | Withdrawn: SPM27 Bayu Partner Lunch</t>
-  </si>
-  <si>
-    <t>On every event the status is shown only as the badge and the read-only Details 'Status' row.
-No 'Withdraw request' button is shown, and there is no button, dropdown or field that changes the status.</t>
-  </si>
-  <si>
     <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder just before this case.
-'SPM27 Bayu Town Hall' is Submitted with no coordinator; 'SPM27 Bayu Contractor Briefing' is Under review with coordinator Hui Shan Neo.
-Team decision: see TC03.</t>
+'SPM27 Bayu Contractor Briefing' is Under review with coordinator Hui Shan Neo; 'SPM27 Bayu Supplier Day' is Approved with coordinator Hui Shan Neo.
+Withdrawal follows customer clarification #103: the organiser asks the Event Coordinator outside the system, and the assigned coordinator records the withdrawal while the request is Under review. Withdrawn is final.</t>
   </si>
   <si>
     <t>1. Log in as Grace Lim (grace.lim@connectsphere.com / password123)
-2. Click 'All Events' and open 'SPM27 Bayu Town Hall'
-3. Look for a 'Withdraw request' button
-4. Log out and log in as Hui Shan Neo (huishan.neo@connectsphere.com / password123)
-5. Click 'All Events' and open 'SPM27 Bayu Contractor Briefing'
-6. Look for a 'Withdraw request' button</t>
-  </si>
-  <si>
-    <t>Event Operations Manager: grace.lim@connectsphere.com / password123 | Event Coordinator: huishan.neo@connectsphere.com / password123</t>
-  </si>
-  <si>
-    <t>Neither user sees a 'Withdraw request' button.</t>
+2. Click 'All Events' in the sidebar
+3. Open 'SPM27 Bayu Contractor Briefing'
+4. Log out and log in as Daniel Tan (daniel.tan@connectsphere.com / password123)
+5. Click 'All Events' in the sidebar
+6. Open 'SPM27 Bayu Contractor Briefing'
+7. Log out and log in as Hui Shan Neo (huishan.neo@connectsphere.com / password123)
+8. Click 'All Events' in the sidebar
+9. Open 'SPM27 Bayu Supplier Day'</t>
+  </si>
+  <si>
+    <t>Event Operations Manager: Grace Lim | Unassigned Event Coordinator: Daniel Tan | Assigned Event Coordinator: Hui Shan Neo | Under review: SPM27 Bayu Contractor Briefing | Approved: SPM27 Bayu Supplier Day</t>
+  </si>
+  <si>
+    <t>Step 3: No 'Record withdrawal' button is shown.
+Step 6: No 'Record withdrawal' button is shown.
+Step 9: No 'Record withdrawal' button is shown, because the event is past review.</t>
   </si>
   <si>
     <t>Test data loaded: run `npm run fixtures:spm27` from the project folder if it has not been run for this test pass.
-'SPM27 Bayu Partner Lunch' was withdrawn while Submitted (no coordinator); 'SPM27 Bayu Wind Farm Tour' was withdrawn while Under review (coordinator Hui Shan Neo).</t>
-  </si>
-  <si>
-    <t>1. Log in as Grace Lim (grace.lim@connectsphere.com / password123)
-2. Click 'Assignments' in the sidebar and look for 'SPM27 Bayu Partner Lunch' in 'Awaiting assignment'
-3. Click 'All Events' and open 'SPM27 Bayu Partner Lunch'
-4. Log out and log in as Hui Shan Neo (huishan.neo@connectsphere.com / password123)
-5. Click 'All Events' and open 'SPM27 Bayu Wind Farm Tour'
-6. Open the 'Equipment' tab</t>
-  </si>
-  <si>
-    <t>Withdrawn from Submitted: SPM27 Bayu Partner Lunch | Withdrawn from Under review: SPM27 Bayu Wind Farm Tour</t>
-  </si>
-  <si>
-    <t>'SPM27 Bayu Partner Lunch' is not in the 'Awaiting assignment' list, and its event page has no 'Assign a coordinator' card.
-The Equipment tab of 'SPM27 Bayu Wind Farm Tour' shows 'This event is withdrawn — equipment requirements can no longer be changed.' with no add, edit or remove controls.</t>
+'SPM27 Bayu Partner Lunch' and 'SPM27 Bayu Wind Farm Tour' were withdrawn while Under review (coordinator Hui Shan Neo).</t>
+  </si>
+  <si>
+    <t>1. Log in as Hui Shan Neo (huishan.neo@connectsphere.com / password123)
+2. Click 'Review Queue' in the sidebar
+3. Click 'All Events' in the sidebar
+4. Open 'SPM27 Bayu Wind Farm Tour'
+5. Open the 'Equipment' tab</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Sammi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click 'My Events' in the sidebar
+2. Open 'SPM27 Bayu Safety Briefing'
+3. Click 'My Events' in the sidebar
+4. Open 'SPM27 Bayu Contractor Briefing'
+5. Click 'My Events' in the sidebar
+6. Open 'SPM27 Bayu Supplier Day'
+7. Click 'My Events' in the sidebar
+8. Open 'SPM27 Bayu Leadership Retreat'
+</t>
+  </si>
+  <si>
+    <t>Submitted: SPM27 Bayu Safety Briefing | Under review: SPM27 Bayu Contractor Briefing | Approved: SPM27 Bayu Supplier Day | Planning: SPM27 Bayu Leadership Retreat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 2: On 'SPM27 Bayu Safety Briefing', the status is shown only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
+Step 4: On 'SPM27 Bayu Contractor Briefing', the status is shown only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
+Step 6: On 'SPM27 Bayu Supplier Day', the status is shown only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
+Step 8: On 'SPM27 Bayu Leadership Retreat', the status is shown only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
+</t>
+  </si>
+  <si>
+    <t>Withdrawn: SPM27 Bayu Wind Farm Tour</t>
+  </si>
+  <si>
+    <t>Step 2:  'SPM27 Bayu Wind Farm Tour' is not listed.
+Step 4: The badge reads 'Withdrawn' and there is no 'Record withdrawal' or 'Review request' action.
+Step 5: The tab shows 'This event is withdrawn — equipment requirements can no longer be changed.' with no add, edit or remove controls.</t>
   </si>
 </sst>
 </file>
@@ -547,12 +567,12 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -770,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -785,7 +805,7 @@
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="14"/>
@@ -793,7 +813,7 @@
       <c r="E1" s="14"/>
       <c r="F1" s="15"/>
     </row>
-    <row r="3" spans="1:6" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="13" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
@@ -813,7 +833,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>8</v>
       </c>
@@ -833,7 +853,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
@@ -853,7 +873,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>18</v>
       </c>
@@ -893,7 +913,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>28</v>
       </c>
@@ -913,7 +933,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
@@ -924,7 +944,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>22</v>
@@ -933,15 +953,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="25" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>39</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>21</v>
@@ -953,110 +973,102 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="14" spans="1:6" ht="13" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="13" spans="1:6" ht="13" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>40</v>
       </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="B14" s="13" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="15"/>
       <c r="E14" s="13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" s="15"/>
     </row>
-    <row r="15" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>44</v>
+        <v>21</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="15"/>
-      <c r="E15" s="16" t="s">
-        <v>45</v>
+      <c r="E15" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="F15" s="15"/>
     </row>
-    <row r="16" spans="1:6" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="16" t="s">
-        <v>47</v>
+      <c r="E16" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" spans="1:6" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>48</v>
+        <v>31</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="15"/>
-      <c r="E17" s="16" t="s">
-        <v>49</v>
+      <c r="E17" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F17" s="15"/>
     </row>
-    <row r="18" spans="1:6" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F18" s="15"/>
-    </row>
-    <row r="20" spans="1:6" ht="193" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="19" spans="1:6" ht="206.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B19" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B19:F19"/>
     <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B16:D16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" location="'TC01'!A1" display="TC01" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1072,132 +1084,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="56.81640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="12">
-        <v>46297</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:3" ht="100" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="12">
-        <v>46297</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1209,7 +1095,7 @@
     <col min="2" max="2" width="56.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -1220,39 +1106,39 @@
         <v>3</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1263,7 +1149,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>64</v>
       </c>
@@ -1271,48 +1157,48 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="B15" s="12">
         <v>46297</v>
@@ -1323,7 +1209,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1335,7 +1221,7 @@
     <col min="2" max="2" width="56.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -1346,23 +1232,23 @@
         <v>3</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="152.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1370,15 +1256,15 @@
         <v>58</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1389,7 +1275,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>64</v>
       </c>
@@ -1397,48 +1283,48 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="50" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="B15" s="12">
         <v>46297</v>
@@ -1449,7 +1335,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1461,7 +1347,7 @@
     <col min="2" max="2" width="56.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -1472,15 +1358,15 @@
         <v>3</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="112" customHeight="1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="139" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1488,23 +1374,23 @@
         <v>56</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1515,7 +1401,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>64</v>
       </c>
@@ -1523,48 +1409,48 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="50" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="B15" s="12">
         <v>46297</v>
@@ -1575,7 +1461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1587,7 +1473,7 @@
     <col min="2" max="2" width="56.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -1598,39 +1484,39 @@
         <v>3</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="179.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1641,7 +1527,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>64</v>
       </c>
@@ -1649,48 +1535,48 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="50" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="50" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="B15" s="12">
         <v>46297</v>
@@ -1701,7 +1587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1713,7 +1599,7 @@
     <col min="2" max="2" width="56.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -1724,39 +1610,39 @@
         <v>3</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="44.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="212.5" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1767,7 +1653,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>64</v>
       </c>
@@ -1775,48 +1661,48 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="212.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="B15" s="12">
         <v>46297</v>
@@ -1827,7 +1713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1839,7 +1725,7 @@
     <col min="2" max="2" width="56.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -1850,23 +1736,149 @@
         <v>3</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="71.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="125.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="166" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>94</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:3" ht="50" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="12">
+        <v>46297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
+    <col min="2" max="2" width="56.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="31" customHeight="1" x14ac:dyDescent="0.25">
@@ -1874,15 +1886,15 @@
         <v>58</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="85" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="98.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>60</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1893,7 +1905,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>64</v>
       </c>
@@ -1901,48 +1913,48 @@
         <v>46297</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
     </row>
-    <row r="11" spans="1:3" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>72</v>
       </c>
       <c r="B15" s="12">
         <v>46297</v>

--- a/docs/test-cases/SPM-27_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-27_Test_Cases.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -46,6 +46,9 @@
       <color rgb="FF1155CC"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -131,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -178,6 +181,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,12 +476,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="19">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>SPM-27: As an Event Organiser, I want to view the current status of my event request so that I know how far it has progressed</t>
         </is>
@@ -487,32 +493,32 @@
     </row>
     <row r="2" ht="12" customHeight="1" s="19"/>
     <row r="3" ht="12" customHeight="1" s="19">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -539,27 +545,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC01</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>My Events shows each of the organiser's events with its current status badge</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>AC1, AC3</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -578,38 +584,42 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC02</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Event page status changes after another role acts on the event</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t>AC1, AC2</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G5" s="23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H5" s="23" t="n"/>
-      <c r="I5" s="23" t="n"/>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="12" customHeight="1" s="19">
       <c r="A6" s="13" t="inlineStr">
@@ -617,27 +627,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC03</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Choosing 'Keep request' in the withdrawal dialog leaves the status unchanged</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -656,27 +666,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC04</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Coordinator records a withdrawal and the organiser sees Withdrawn</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>AC2, AC3</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -695,27 +705,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC05</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Organiser has no way to change the status of their event</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -734,38 +744,42 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC06</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Only the assigned coordinator is offered 'Record withdrawal'</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H9" s="23" t="n"/>
-      <c r="I9" s="23" t="n"/>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="12" customHeight="1" s="19">
       <c r="A10" s="13" t="inlineStr">
@@ -773,27 +787,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC07</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>A withdrawn request is closed for the Operations Manager and the coordinator</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -809,19 +823,19 @@
     <row r="11" ht="12" customHeight="1" s="19"/>
     <row r="12" ht="12" customHeight="1" s="19"/>
     <row r="13" ht="12" customHeight="1" s="19">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C13" s="20" t="n"/>
       <c r="D13" s="21" t="n"/>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -829,19 +843,19 @@
       <c r="F13" s="21" t="n"/>
     </row>
     <row r="14" ht="30.75" customHeight="1" s="19">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>The Event Organiser can view the current status of their event.</t>
         </is>
       </c>
       <c r="C14" s="20" t="n"/>
       <c r="D14" s="21" t="n"/>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC01
 SPM-27-TC02</t>
@@ -850,19 +864,19 @@
       <c r="F14" s="21" t="n"/>
     </row>
     <row r="15" ht="71.25" customHeight="1" s="19">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>The status reflects the latest action performed on the event.</t>
         </is>
       </c>
       <c r="C15" s="20" t="n"/>
       <c r="D15" s="21" t="n"/>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC02
 SPM-27-TC03
@@ -874,19 +888,19 @@
       <c r="F15" s="21" t="n"/>
     </row>
     <row r="16" ht="44.25" customHeight="1" s="19">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>The system displays appropriate statuses such as Submitted, Under Review, Approved, Planning, Confirmed, Completed, Rejected, Postponed, Withdrawn or Cancelled.</t>
         </is>
       </c>
       <c r="C16" s="20" t="n"/>
       <c r="D16" s="21" t="n"/>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC01
 SPM-27-TC04</t>
@@ -895,19 +909,19 @@
       <c r="F16" s="21" t="n"/>
     </row>
     <row r="17" ht="17.25" customHeight="1" s="19">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>The Event Organiser cannot manually change the event status.</t>
         </is>
       </c>
       <c r="C17" s="20" t="n"/>
       <c r="D17" s="21" t="n"/>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC05</t>
         </is>
@@ -916,12 +930,12 @@
     </row>
     <row r="18" ht="12" customHeight="1" s="19"/>
     <row r="19" ht="206.25" customHeight="1" s="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>src/lib/statuses.ts
 src/lib/permissions.ts
@@ -1983,7 +1997,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC01</t>
         </is>
@@ -1995,7 +2009,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder just before this case.
 Logged in as Hakim Zulkifli (hakim.zulkifli@bayuenergypa.com / password123), Event Organiser, Bayu Energy Partners.</t>
@@ -2008,7 +2022,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'My Events' in the sidebar</t>
         </is>
@@ -2020,7 +2034,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>SPM27 Bayu Safety Briefing: Submitted | SPM27 Bayu Investor Day: Submitted | SPM27 Bayu Town Hall: Submitted | SPM27 Bayu Grid Workshop: Under review | SPM27 Bayu Contractor Briefing: Under review | SPM27 Bayu Supplier Day: Approved | SPM27 Bayu Leadership Retreat: Planning | SPM27 Bayu Annual Conference: Confirmed | SPM27 Bayu Graduate Induction: Completed | SPM27 Bayu Overnight Site Visit: Rejected | SPM27 Bayu Community Fair: Postponed | SPM27 Bayu Partner Lunch: Withdrawn | SPM27 Bayu Wind Farm Tour: Withdrawn | SPM27 Bayu Product Showcase: Cancelled</t>
         </is>
@@ -2032,7 +2046,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 1: Each of the 14 SPM27 events shows a coloured status badge with exactly the label listed in Test data, so all 10 statuses appear: Submitted, Under review, Approved, Planning, Confirmed, Completed, Rejected, Postponed, Withdrawn, Cancelled (some on more than one event). No status is shown as a raw value such as 'under_review'. Only Bayu Energy Partners events are listed; no other company's events appear.</t>
         </is>
@@ -2044,7 +2058,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -2076,7 +2090,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 1: Each of the 14 SPM27 events shows a coloured status badge with exactly the label listed in Test data, so all 10 statuses appear: Submitted, Under review, Approved, Planning, Confirmed, Completed, Rejected, Postponed, Withdrawn, Cancelled (some on more than one event). No status is shown as a raw value such as 'under_review'. Only Bayu Energy Partners events are listed; no other company's events appear.</t>
         </is>
@@ -2144,7 +2158,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 1: Each of the 14 SPM27 events shows a coloured status badge with exactly the label listed in Test data, so all 10 statuses appear: Submitted, Under review, Approved, Planning, Confirmed, Completed, Rejected, Postponed, Withdrawn, Cancelled (some on more than one event). No status is shown as a raw value such as 'under_review'. Only Bayu Energy Partners events are listed; no other company's events appear.</t>
         </is>
@@ -3185,7 +3199,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.88" customWidth="1" style="19" min="1" max="1"/>
@@ -3193,33 +3207,40 @@
     <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="19">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="19">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="19">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>SPM-27-TC02</t>
-        </is>
-      </c>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="84.75" customHeight="1" s="19">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SPM-27-TC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="152.25" customHeight="1" s="19">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder before and after this case.
 'SPM27 Bayu Investor Day' is Submitted with no coordinator.
@@ -3227,13 +3248,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="152.25" customHeight="1" s="19">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5" ht="17.25" customHeight="1" s="19">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Log in as Hakim Zulkifli
 2. Click 'My Events' in the sidebar
@@ -3248,192 +3269,191 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" s="19">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Event: SPM27 Bayu Investor Day | Coordinator: Hui Shan Neo</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="57.75" customHeight="1" s="19">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event: SPM27 Bayu Investor Day | Coordinator: Hui Shan Neo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="19">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 3: The badge under the title and the Details 'Status' row both read 'Submitted'.
 Step 10: The badge and the Details 'Status' row both read 'Under review'.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="19">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="19">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="19">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46297</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="19"/>
-    <row r="10" ht="15.75" customHeight="1" s="19">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="19"/>
+    <row r="11" ht="15.75" customHeight="1" s="19">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="19">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 3: The badge under the title and the Details 'Status' row both read 'Submitted'.
 Step 10: The badge and the Details 'Status' row both read 'Under review', with Hui Shan Neo under Coordinator</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="19">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="19">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="19">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Sammi</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="19">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="19">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B16" s="17" t="n">
         <v>46297</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="19"/>
     <row r="17" ht="15.75" customHeight="1" s="19"/>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="19"/>
+    <row r="19" ht="15.75" customHeight="1" s="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="B19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="19">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Step 3: The badge under the title and the Details 'Status' row both read 'Submitted'.
 Step 10: The badge and the Details 'Status' row both read 'Under review', with Hui Shan Neo under Coordinator</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="19">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="19">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Janelle</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="19">
       <c r="A23" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="19">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B24" s="17" t="n">
         <v>46298</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="15.75" customHeight="1" s="19"/>
     <row r="26" ht="15.75" customHeight="1" s="19"/>
     <row r="27" ht="15.75" customHeight="1" s="19"/>
@@ -4411,6 +4431,9 @@
     <row r="999" ht="15.75" customHeight="1" s="19"/>
     <row r="1000" ht="15.75" customHeight="1" s="19"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -4444,7 +4467,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC03</t>
         </is>
@@ -4456,7 +4479,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder just before this case.
 'SPM27 Bayu Grid Workshop' is Under review, coordinator Hui Shan Neo.
@@ -4471,7 +4494,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Open 'SPM27 Bayu Grid Workshop'
@@ -4487,7 +4510,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM27 Bayu Grid Workshop (Under review)</t>
         </is>
@@ -4499,7 +4522,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 3: A dialog titled 'Record this withdrawal?' appears.
 Step 4: The dialog closes.
@@ -4513,7 +4536,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -4545,7 +4568,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 3: A dialog titled 'Record this withdrawal?' appears.
 Step 4: The dialog closes.
@@ -4615,7 +4638,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 3: A dialog titled 'Record this withdrawal?' appears.
 Step 4: The dialog closes.
@@ -5680,7 +5703,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC04</t>
         </is>
@@ -5692,7 +5715,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder before and after this case (SPM-27-TC03 does not change the data, so this case can run straight after it).
 'SPM27 Bayu Grid Workshop' is Under review, coordinator Hui Shan Neo.
@@ -5707,7 +5730,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Log in as Hui Shan Neo
 2. Click 'All Events' in the sidebar
@@ -5726,7 +5749,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Event: SPM27 Bayu Grid Workshop (Under review)</t>
         </is>
@@ -5738,7 +5761,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 5: The message 'The withdrawal has been recorded.' is shown, the badge changes to 'Withdrawn' and the 'Record withdrawal' button is gone.
 Step 8: The badge and the Details 'Status' row read 'Withdrawn'.</t>
@@ -5751,7 +5774,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -5783,7 +5806,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 5: The message 'The withdrawal has been recorded.' is shown, the badge changes to 'Withdrawn' and the 'Record withdrawal' button is gone.
 Step 8: The badge and the Details 'Status' row read 'Withdrawn'.</t>
@@ -5852,7 +5875,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 5: The message 'The withdrawal has been recorded.' is shown, an alert "The withdrawal has been recorded." is shown, the badge changes to 'Withdrawn' and the 'Record withdrawal' button is gone.
 Step 8: The badge and the Details 'Status' row read 'Withdrawn'.</t>
@@ -6916,7 +6939,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC05</t>
         </is>
@@ -6928,7 +6951,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm27` from the project folder if it has not been run for this test pass.
 Logged in as Hakim Zulkifli (hakim.zulkifli@bayuenergypa.com / password123).</t>
@@ -6941,7 +6964,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Click 'My Events' in the sidebar
 2. Open 'SPM27 Bayu Safety Briefing'
@@ -6961,7 +6984,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Submitted: SPM27 Bayu Safety Briefing | Under review: SPM27 Bayu Contractor Briefing | Approved: SPM27 Bayu Supplier Day | Planning: SPM27 Bayu Leadership Retreat</t>
         </is>
@@ -6973,7 +6996,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Step 2: On 'SPM27 Bayu Safety Briefing', the status is shown only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
 Step 4: On 'SPM27 Bayu Contractor Briefing', the status is shown only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
@@ -6989,7 +7012,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -7021,7 +7044,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Step 2: On 'SPM27 Bayu Safety Briefing', the status is shown as Submitted and only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
 Step 4: On 'SPM27 Bayu Contractor Briefing', the status is shown as Under review and only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
@@ -7093,7 +7116,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Step 2: On 'SPM27 Bayu Safety Briefing', the status is shown as Submitted and only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
 Step 4: On 'SPM27 Bayu Contractor Briefing', the status is shown as Under review and only as the badge and the read-only Details 'Status' row; there is no 'Record withdrawal' button and no button, dropdown or field that changes the status.
@@ -8138,7 +8161,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.88" customWidth="1" style="19" min="1" max="1"/>
@@ -8146,33 +8169,40 @@
     <col width="12.63" customWidth="1" style="19" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="19">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="19">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="19">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="19">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>SPM-27-TC06</t>
-        </is>
-      </c>
+      <c r="B2" s="4" t="n"/>
     </row>
     <row r="3" ht="125.25" customHeight="1" s="19">
       <c r="A3" s="5" t="inlineStr">
         <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SPM-27-TC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="165.75" customHeight="1" s="19">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Test data freshly loaded: run `npm run fixtures:spm27` from the project folder just before this case.
 'SPM27 Bayu Contractor Briefing' is Under review with coordinator Hui Shan Neo; 'SPM27 Bayu Supplier Day' is Approved with coordinator Hui Shan Neo.
@@ -8180,13 +8210,13 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="165.75" customHeight="1" s="19">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="5" ht="57.75" customHeight="1" s="19">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>1. Log in as Grace Lim (grace.lim@connectsphere.com / password123)
 2. Click 'All Events' in the sidebar
@@ -8200,25 +8230,25 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="57.75" customHeight="1" s="19">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Test Data</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Event Operations Manager: Grace Lim | Unassigned Event Coordinator: Daniel Tan | Assigned Event Coordinator: Hui Shan Neo | Under review: SPM27 Bayu Contractor Briefing | Approved: SPM27 Bayu Supplier Day</t>
-        </is>
-      </c>
-    </row>
     <row r="6" ht="57.75" customHeight="1" s="19">
       <c r="A6" s="5" t="inlineStr">
         <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Event Operations Manager: Grace Lim | Unassigned Event Coordinator: Daniel Tan | Assigned Event Coordinator: Hui Shan Neo | Under review: SPM27 Bayu Contractor Briefing | Approved: SPM27 Bayu Supplier Day</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="19">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Step 3: No 'Record withdrawal' button is shown.
 Step 6: No 'Record withdrawal' button is shown.
@@ -8226,45 +8256,45 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="19">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>Sammi Chua</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="15.75" customHeight="1" s="19">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Sammi Chua</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" s="19">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B9" s="17" t="n">
         <v>46297</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="19"/>
-    <row r="10" ht="15.75" customHeight="1" s="19">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="15.75" customHeight="1" s="19"/>
+    <row r="11" ht="15.75" customHeight="1" s="19">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" s="19">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" s="19">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Step 3: No 'Record withdrawal' button is shown.
 Step 6: No 'Record withdrawal' button is shown.
@@ -8272,69 +8302,69 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1" s="19">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="13" ht="15.75" customHeight="1" s="19">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="19">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Sammi</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="19">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Sammi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" s="19">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B16" s="17" t="n">
         <v>46297</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="19"/>
     <row r="17" ht="15.75" customHeight="1" s="19"/>
-    <row r="18" ht="15.75" customHeight="1" s="19">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="19"/>
+    <row r="19" ht="15.75" customHeight="1" s="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="B19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="19">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Step 3: No 'Record withdrawal' button is shown.
 Step 6: No 'Record withdrawal' button is shown.
@@ -8342,53 +8372,52 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="19">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1" s="19">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="19">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Executed by</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Janelle</t>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="19">
       <c r="A23" s="16" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Janelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="19">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B24" s="17" t="n">
         <v>46298</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="19"/>
     <row r="25" ht="15.75" customHeight="1" s="19"/>
     <row r="26" ht="15.75" customHeight="1" s="19"/>
     <row r="27" ht="15.75" customHeight="1" s="19"/>
@@ -9366,6 +9395,9 @@
     <row r="999" ht="15.75" customHeight="1" s="19"/>
     <row r="1000" ht="15.75" customHeight="1" s="19"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -9399,7 +9431,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>SPM-27-TC07</t>
         </is>
@@ -9411,7 +9443,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Test data loaded: run `npm run fixtures:spm27` from the project folder if it has not been run for this test pass.
 'SPM27 Bayu Partner Lunch' and 'SPM27 Bayu Wind Farm Tour' were withdrawn while Under review (coordinator Hui Shan Neo).</t>
@@ -9424,7 +9456,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>1. Log in as Hui Shan Neo (huishan.neo@connectsphere.com / password123)
 2. Click 'Review Queue' in the sidebar
@@ -9440,7 +9472,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Withdrawn: SPM27 Bayu Wind Farm Tour</t>
         </is>
@@ -9452,7 +9484,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Step 2:  'SPM27 Bayu Wind Farm Tour' is not listed.
 Step 4: The badge reads 'Withdrawn' and there is no 'Record withdrawal' or 'Review request' action.
@@ -9466,7 +9498,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Sammi Chua</t>
         </is>
@@ -9498,7 +9530,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Step 2:  'SPM27 Bayu Wind Farm Tour' is not listed.
 Step 4: The badge reads 'Withdrawn' and there is no 'Record withdrawal' or 'Review request' action.
@@ -9568,7 +9600,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Step 2:  'SPM27 Bayu Wind Farm Tour' is not listed.
 Step 4: The badge reads 'Withdrawn' and there is no 'Record withdrawal' or 'Review request' action.
